--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1539,6 +1539,312 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125194951</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592692</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6985083</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125194947</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592692</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6985083</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125194962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592702</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6985083</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194951</v>
+        <v>125194962</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592692</v>
+        <v>592702</v>
       </c>
       <c r="R10" t="n">
         <v>6985083</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194947</v>
+        <v>125194951</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194962</v>
+        <v>125194947</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592702</v>
+        <v>592692</v>
       </c>
       <c r="R12" t="n">
         <v>6985083</v>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194962</v>
+        <v>125194951</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592702</v>
+        <v>592692</v>
       </c>
       <c r="R10" t="n">
         <v>6985083</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194951</v>
+        <v>125194947</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194947</v>
+        <v>125194962</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592692</v>
+        <v>592702</v>
       </c>
       <c r="R12" t="n">
         <v>6985083</v>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194962</v>
+        <v>125194947</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592702</v>
+        <v>592692</v>
       </c>
       <c r="R10" t="n">
         <v>6985083</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194951</v>
+        <v>125194962</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592692</v>
+        <v>592702</v>
       </c>
       <c r="R11" t="n">
         <v>6985083</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194947</v>
+        <v>125194951</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>125194947</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194962</v>
+        <v>125194951</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592702</v>
+        <v>592692</v>
       </c>
       <c r="R11" t="n">
         <v>6985083</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194951</v>
+        <v>125194962</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592692</v>
+        <v>592702</v>
       </c>
       <c r="R12" t="n">
         <v>6985083</v>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194947</v>
+        <v>125194951</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194951</v>
+        <v>125194962</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592692</v>
+        <v>592702</v>
       </c>
       <c r="R11" t="n">
         <v>6985083</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194962</v>
+        <v>125194947</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592702</v>
+        <v>592692</v>
       </c>
       <c r="R12" t="n">
         <v>6985083</v>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1544,12 +1544,7 @@
         <v>125194951</v>
       </c>
       <c r="B10" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,12 +1641,7 @@
         <v>125194962</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,12 +1738,7 @@
         <v>125194947</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19251-2025 artfynd.xlsx
+++ b/artfynd/A 19251-2025 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>125194951</v>
       </c>
       <c r="B10" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>125194947</v>
       </c>
       <c r="B12" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
